--- a/IRA_flat_singlefolder/Other_Tables.xlsx
+++ b/IRA_flat_singlefolder/Other_Tables.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yavnv\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yavnv\Downloads\IRA_Final_18Sept26_3\IRA_flat_singlefolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0232659D-1E14-4697-BFC7-B19353E90935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4763D4-2B41-40AC-9083-3F0E6C2D44E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{6C3792BD-ED8C-4773-AE5D-109238BEF1B8}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="238">
   <si>
     <t>Country</t>
   </si>
@@ -737,6 +737,12 @@
   </si>
   <si>
     <t>Shortfall against real estate:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Amount</t>
+  </si>
+  <si>
+    <t>client</t>
   </si>
 </sst>
 </file>
@@ -834,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -862,6 +868,40 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -874,41 +914,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1232,10 +1241,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="29"/>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
     </row>
@@ -1530,10 +1539,10 @@
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="15"/>
+      <c r="C40" s="29"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
@@ -1824,10 +1833,10 @@
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C78" s="15"/>
+      <c r="C78" s="29"/>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
@@ -2118,10 +2127,10 @@
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="15" t="s">
+      <c r="B116" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C116" s="15"/>
+      <c r="C116" s="29"/>
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
     </row>
@@ -2416,22 +2425,22 @@
       </c>
     </row>
     <row r="156" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B156" s="16" t="s">
+      <c r="B156" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C156" s="16"/>
-      <c r="D156" s="16"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="16"/>
-      <c r="G156" s="16"/>
-      <c r="H156" s="16"/>
-      <c r="I156" s="16"/>
-      <c r="J156" s="16"/>
-      <c r="K156" s="16"/>
-      <c r="L156" s="16"/>
-      <c r="M156" s="16"/>
-      <c r="N156" s="16"/>
-      <c r="O156" s="16"/>
+      <c r="C156" s="30"/>
+      <c r="D156" s="30"/>
+      <c r="E156" s="30"/>
+      <c r="F156" s="30"/>
+      <c r="G156" s="30"/>
+      <c r="H156" s="30"/>
+      <c r="I156" s="30"/>
+      <c r="J156" s="30"/>
+      <c r="K156" s="30"/>
+      <c r="L156" s="30"/>
+      <c r="M156" s="30"/>
+      <c r="N156" s="30"/>
+      <c r="O156" s="30"/>
       <c r="P156" s="2"/>
     </row>
     <row r="157" spans="2:16" x14ac:dyDescent="0.3">
@@ -3495,22 +3504,22 @@
       </c>
     </row>
     <row r="195" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B195" s="18" t="s">
+      <c r="B195" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C195" s="18"/>
-      <c r="D195" s="18"/>
-      <c r="E195" s="18"/>
-      <c r="F195" s="18"/>
-      <c r="G195" s="18"/>
-      <c r="H195" s="18"/>
-      <c r="I195" s="18"/>
-      <c r="J195" s="18"/>
-      <c r="K195" s="18"/>
-      <c r="L195" s="18"/>
-      <c r="M195" s="18"/>
-      <c r="N195" s="18"/>
-      <c r="O195" s="18"/>
+      <c r="C195" s="32"/>
+      <c r="D195" s="32"/>
+      <c r="E195" s="32"/>
+      <c r="F195" s="32"/>
+      <c r="G195" s="32"/>
+      <c r="H195" s="32"/>
+      <c r="I195" s="32"/>
+      <c r="J195" s="32"/>
+      <c r="K195" s="32"/>
+      <c r="L195" s="32"/>
+      <c r="M195" s="32"/>
+      <c r="N195" s="32"/>
+      <c r="O195" s="32"/>
     </row>
     <row r="196" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B196" s="1" t="s">
@@ -4573,22 +4582,22 @@
       </c>
     </row>
     <row r="233" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B233" s="16" t="s">
+      <c r="B233" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="C233" s="16"/>
-      <c r="D233" s="16"/>
-      <c r="E233" s="16"/>
-      <c r="F233" s="16"/>
-      <c r="G233" s="16"/>
-      <c r="H233" s="16"/>
-      <c r="I233" s="16"/>
-      <c r="J233" s="16"/>
-      <c r="K233" s="16"/>
-      <c r="L233" s="16"/>
-      <c r="M233" s="16"/>
-      <c r="N233" s="16"/>
-      <c r="O233" s="16"/>
+      <c r="C233" s="30"/>
+      <c r="D233" s="30"/>
+      <c r="E233" s="30"/>
+      <c r="F233" s="30"/>
+      <c r="G233" s="30"/>
+      <c r="H233" s="30"/>
+      <c r="I233" s="30"/>
+      <c r="J233" s="30"/>
+      <c r="K233" s="30"/>
+      <c r="L233" s="30"/>
+      <c r="M233" s="30"/>
+      <c r="N233" s="30"/>
+      <c r="O233" s="30"/>
       <c r="P233" s="2"/>
     </row>
     <row r="234" spans="2:16" x14ac:dyDescent="0.3">
@@ -5652,22 +5661,22 @@
       </c>
     </row>
     <row r="272" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B272" s="16" t="s">
+      <c r="B272" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="C272" s="16"/>
-      <c r="D272" s="16"/>
-      <c r="E272" s="16"/>
-      <c r="F272" s="16"/>
-      <c r="G272" s="16"/>
-      <c r="H272" s="16"/>
-      <c r="I272" s="16"/>
-      <c r="J272" s="16"/>
-      <c r="K272" s="16"/>
-      <c r="L272" s="16"/>
-      <c r="M272" s="16"/>
-      <c r="N272" s="16"/>
-      <c r="O272" s="16"/>
+      <c r="C272" s="30"/>
+      <c r="D272" s="30"/>
+      <c r="E272" s="30"/>
+      <c r="F272" s="30"/>
+      <c r="G272" s="30"/>
+      <c r="H272" s="30"/>
+      <c r="I272" s="30"/>
+      <c r="J272" s="30"/>
+      <c r="K272" s="30"/>
+      <c r="L272" s="30"/>
+      <c r="M272" s="30"/>
+      <c r="N272" s="30"/>
+      <c r="O272" s="30"/>
     </row>
     <row r="273" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B273" s="1" t="s">
@@ -6730,13 +6739,13 @@
       </c>
     </row>
     <row r="311" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B311" s="17" t="s">
+      <c r="B311" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C311" s="17"/>
-      <c r="D311" s="17"/>
-      <c r="E311" s="17"/>
-      <c r="F311" s="17"/>
+      <c r="C311" s="31"/>
+      <c r="D311" s="31"/>
+      <c r="E311" s="31"/>
+      <c r="F311" s="31"/>
     </row>
     <row r="312" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B312" s="5" t="s">
@@ -12259,208 +12268,208 @@
       </c>
     </row>
     <row r="4" spans="2:46" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="20" t="s">
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="20" t="s">
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="20" t="s">
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="20" t="s">
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="20" t="s">
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="21"/>
-      <c r="Z4" s="21"/>
-      <c r="AA4" s="20" t="s">
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
-      <c r="AE4" s="20" t="s">
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="AF4" s="21"/>
-      <c r="AG4" s="21"/>
-      <c r="AH4" s="21"/>
-      <c r="AI4" s="20" t="s">
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="AJ4" s="21"/>
-      <c r="AK4" s="21"/>
-      <c r="AL4" s="21"/>
-      <c r="AM4" s="20" t="s">
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="AN4" s="21"/>
-      <c r="AO4" s="21"/>
-      <c r="AP4" s="21"/>
-      <c r="AQ4" s="20" t="s">
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="AR4" s="21"/>
-      <c r="AS4" s="21"/>
-      <c r="AT4" s="21"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+      <c r="AT4" s="27"/>
     </row>
     <row r="5" spans="2:46" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="19"/>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="N5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="P5" s="22" t="s">
+      <c r="P5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="Q5" s="22" t="s">
+      <c r="Q5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="R5" s="22" t="s">
+      <c r="R5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="S5" s="22" t="s">
+      <c r="S5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="T5" s="22" t="s">
+      <c r="T5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="U5" s="22" t="s">
+      <c r="U5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="V5" s="22" t="s">
+      <c r="V5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="W5" s="22" t="s">
+      <c r="W5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="X5" s="22" t="s">
+      <c r="X5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="Y5" s="22" t="s">
+      <c r="Y5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="Z5" s="22" t="s">
+      <c r="Z5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="AA5" s="22" t="s">
+      <c r="AA5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="AB5" s="22" t="s">
+      <c r="AB5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="AC5" s="22" t="s">
+      <c r="AC5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="AD5" s="22" t="s">
+      <c r="AD5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="AE5" s="22" t="s">
+      <c r="AE5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="AF5" s="22" t="s">
+      <c r="AF5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="AG5" s="22" t="s">
+      <c r="AG5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="AH5" s="22" t="s">
+      <c r="AH5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="AI5" s="22" t="s">
+      <c r="AI5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="AJ5" s="22" t="s">
+      <c r="AJ5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="AK5" s="22" t="s">
+      <c r="AK5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="AL5" s="22" t="s">
+      <c r="AL5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="AM5" s="22" t="s">
+      <c r="AM5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="AN5" s="22" t="s">
+      <c r="AN5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="AO5" s="22" t="s">
+      <c r="AO5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="AP5" s="22" t="s">
+      <c r="AP5" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="AQ5" s="22" t="s">
+      <c r="AQ5" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="AR5" s="22" t="s">
+      <c r="AR5" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="AS5" s="22" t="s">
+      <c r="AS5" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="AT5" s="22" t="s">
+      <c r="AT5" s="15" t="s">
         <v>216</v>
       </c>
     </row>
@@ -12474,7 +12483,7 @@
       <c r="D6" s="2">
         <v>350000</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="16">
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="F6" s="2">
@@ -12531,7 +12540,7 @@
       <c r="D7" s="2">
         <v>5.67</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="16">
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="F7" s="2">
@@ -12588,7 +12597,7 @@
       <c r="D8" s="2">
         <v>1.45</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="16">
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="F8" s="2">
@@ -12645,7 +12654,7 @@
       <c r="D9" s="2">
         <v>2.5</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="16">
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="F9" s="2">
@@ -12693,64 +12702,64 @@
       <c r="AT9" s="2"/>
     </row>
     <row r="10" spans="2:46" x14ac:dyDescent="0.3">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="17">
         <f>SUM(C6:C9)</f>
         <v>144</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="17">
         <f>SUM(D6:D9)</f>
         <v>350009.62</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="18">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="17">
         <f>SUM(F6:F9)</f>
         <v>12.229999999999999</v>
       </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="24"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="24"/>
-      <c r="AA10" s="24"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="24"/>
-      <c r="AH10" s="24"/>
-      <c r="AI10" s="24"/>
-      <c r="AJ10" s="24"/>
-      <c r="AK10" s="24"/>
-      <c r="AL10" s="24"/>
-      <c r="AM10" s="24"/>
-      <c r="AN10" s="24"/>
-      <c r="AO10" s="24"/>
-      <c r="AP10" s="24"/>
-      <c r="AQ10" s="24"/>
-      <c r="AR10" s="24"/>
-      <c r="AS10" s="24"/>
-      <c r="AT10" s="24"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="17"/>
+      <c r="AK10" s="17"/>
+      <c r="AL10" s="17"/>
+      <c r="AM10" s="17"/>
+      <c r="AN10" s="17"/>
+      <c r="AO10" s="17"/>
+      <c r="AP10" s="17"/>
+      <c r="AQ10" s="17"/>
+      <c r="AR10" s="17"/>
+      <c r="AS10" s="17"/>
+      <c r="AT10" s="17"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
@@ -12763,149 +12772,149 @@
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B24" s="31"/>
-      <c r="C24" s="31" t="s">
+      <c r="B24" s="24"/>
+      <c r="C24" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="E24" s="33" t="s">
+      <c r="E24" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="33" t="s">
+      <c r="G24" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="H24" s="33" t="s">
+      <c r="H24" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="I24" s="33" t="s">
+      <c r="I24" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="J24" s="33" t="s">
+      <c r="J24" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="K24" s="33" t="s">
+      <c r="K24" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="L24" s="33" t="s">
+      <c r="L24" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="33" t="s">
+      <c r="M24" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="33" t="s">
+      <c r="N24" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="33" t="s">
+      <c r="O24" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="P24" s="33" t="s">
+      <c r="P24" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="Q24" s="33" t="s">
+      <c r="Q24" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="33" t="s">
+      <c r="R24" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="S24" s="33" t="s">
+      <c r="S24" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="T24" s="33" t="s">
+      <c r="T24" s="23" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33" t="s">
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="G25" s="33" t="s">
+      <c r="G25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="H25" s="33" t="s">
+      <c r="H25" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="I25" s="33" t="s">
+      <c r="I25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="J25" s="33" t="s">
+      <c r="J25" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="L25" s="33" t="s">
+      <c r="L25" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="M25" s="33" t="s">
+      <c r="M25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="N25" s="33" t="s">
+      <c r="N25" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="O25" s="33" t="s">
+      <c r="O25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="P25" s="33" t="s">
+      <c r="P25" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="Q25" s="33" t="s">
+      <c r="Q25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="R25" s="33" t="s">
+      <c r="R25" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="S25" s="33" t="s">
+      <c r="S25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="T25" s="33" t="s">
+      <c r="T25" s="23" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33" t="s">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33" t="s">
+      <c r="G26" s="23"/>
+      <c r="H26" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33" t="s">
+      <c r="I26" s="23"/>
+      <c r="J26" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33" t="s">
+      <c r="K26" s="23"/>
+      <c r="L26" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33" t="s">
+      <c r="M26" s="23"/>
+      <c r="N26" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33" t="s">
+      <c r="O26" s="23"/>
+      <c r="P26" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33" t="s">
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33" t="s">
+      <c r="S26" s="23"/>
+      <c r="T26" s="23" t="s">
         <v>232</v>
       </c>
     </row>
@@ -12913,58 +12922,58 @@
       <c r="B27" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="19">
         <v>86</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="20">
         <v>12480</v>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="19">
         <v>14</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="20">
         <v>2150</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="19">
         <v>11</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="20">
         <v>1680</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="19">
         <v>16</v>
       </c>
-      <c r="J27" s="28">
+      <c r="J27" s="20">
         <v>2420</v>
       </c>
-      <c r="K27" s="27">
+      <c r="K27" s="19">
         <v>7</v>
       </c>
-      <c r="L27" s="27">
+      <c r="L27" s="19">
         <v>980</v>
       </c>
-      <c r="M27" s="27">
+      <c r="M27" s="19">
         <v>13</v>
       </c>
-      <c r="N27" s="28">
+      <c r="N27" s="20">
         <v>1740</v>
       </c>
-      <c r="O27" s="27">
+      <c r="O27" s="19">
         <v>8</v>
       </c>
-      <c r="P27" s="28">
+      <c r="P27" s="20">
         <v>1120</v>
       </c>
-      <c r="Q27" s="27">
+      <c r="Q27" s="19">
         <v>9</v>
       </c>
-      <c r="R27" s="28">
+      <c r="R27" s="20">
         <v>1390</v>
       </c>
-      <c r="S27" s="27">
+      <c r="S27" s="19">
         <v>8</v>
       </c>
-      <c r="T27" s="28">
+      <c r="T27" s="20">
         <v>1000</v>
       </c>
     </row>
@@ -12972,58 +12981,58 @@
       <c r="B28" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="19">
         <v>52</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="20">
         <v>7860</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="19">
         <v>9</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="20">
         <v>1240</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="19">
         <v>7</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="19">
         <v>980</v>
       </c>
-      <c r="I28" s="27">
-        <v>10</v>
-      </c>
-      <c r="J28" s="28">
+      <c r="I28" s="19">
+        <v>10</v>
+      </c>
+      <c r="J28" s="20">
         <v>1620</v>
       </c>
-      <c r="K28" s="27">
+      <c r="K28" s="19">
         <v>4</v>
       </c>
-      <c r="L28" s="27">
+      <c r="L28" s="19">
         <v>560</v>
       </c>
-      <c r="M28" s="27">
+      <c r="M28" s="19">
         <v>8</v>
       </c>
-      <c r="N28" s="28">
+      <c r="N28" s="20">
         <v>1050</v>
       </c>
-      <c r="O28" s="27">
+      <c r="O28" s="19">
         <v>5</v>
       </c>
-      <c r="P28" s="27">
+      <c r="P28" s="19">
         <v>710</v>
       </c>
-      <c r="Q28" s="27">
+      <c r="Q28" s="19">
         <v>5</v>
       </c>
-      <c r="R28" s="27">
+      <c r="R28" s="19">
         <v>820</v>
       </c>
-      <c r="S28" s="27">
+      <c r="S28" s="19">
         <v>4</v>
       </c>
-      <c r="T28" s="27">
+      <c r="T28" s="19">
         <v>880</v>
       </c>
     </row>
@@ -13031,58 +13040,58 @@
       <c r="B29" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="19">
         <v>31</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="20">
         <v>5275</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="19">
         <v>5</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="19">
         <v>840</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="19">
         <v>4</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="19">
         <v>620</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="19">
         <v>7</v>
       </c>
-      <c r="J29" s="28">
+      <c r="J29" s="20">
         <v>1150</v>
       </c>
-      <c r="K29" s="27">
+      <c r="K29" s="19">
         <v>3</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="19">
         <v>410</v>
       </c>
-      <c r="M29" s="27">
+      <c r="M29" s="19">
         <v>5</v>
       </c>
-      <c r="N29" s="27">
+      <c r="N29" s="19">
         <v>720</v>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="19">
         <v>2</v>
       </c>
-      <c r="P29" s="27">
+      <c r="P29" s="19">
         <v>360</v>
       </c>
-      <c r="Q29" s="27">
+      <c r="Q29" s="19">
         <v>3</v>
       </c>
-      <c r="R29" s="27">
+      <c r="R29" s="19">
         <v>515</v>
       </c>
-      <c r="S29" s="27">
+      <c r="S29" s="19">
         <v>2</v>
       </c>
-      <c r="T29" s="27">
+      <c r="T29" s="19">
         <v>660</v>
       </c>
     </row>
@@ -13090,58 +13099,58 @@
       <c r="B30" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="19">
         <v>18</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="20">
         <v>3140</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="19">
         <v>3</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="19">
         <v>510</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="19">
         <v>2</v>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="19">
         <v>380</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="19">
         <v>4</v>
       </c>
-      <c r="J30" s="27">
+      <c r="J30" s="19">
         <v>720</v>
       </c>
-      <c r="K30" s="27">
+      <c r="K30" s="19">
         <v>2</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="19">
         <v>290</v>
       </c>
-      <c r="M30" s="27">
+      <c r="M30" s="19">
         <v>3</v>
       </c>
-      <c r="N30" s="27">
+      <c r="N30" s="19">
         <v>460</v>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="19">
         <v>1</v>
       </c>
-      <c r="P30" s="27">
+      <c r="P30" s="19">
         <v>190</v>
       </c>
-      <c r="Q30" s="27">
+      <c r="Q30" s="19">
         <v>2</v>
       </c>
-      <c r="R30" s="27">
+      <c r="R30" s="19">
         <v>310</v>
       </c>
-      <c r="S30" s="27">
+      <c r="S30" s="19">
         <v>1</v>
       </c>
-      <c r="T30" s="27">
+      <c r="T30" s="19">
         <v>280</v>
       </c>
     </row>
@@ -13149,359 +13158,330 @@
       <c r="B31" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="21">
         <v>187</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="22">
         <v>28755</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="21">
         <v>31</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="22">
         <v>4740</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="21">
         <v>24</v>
       </c>
-      <c r="H31" s="30">
+      <c r="H31" s="22">
         <v>3660</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="21">
         <v>37</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="22">
         <v>5910</v>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="21">
         <v>16</v>
       </c>
-      <c r="L31" s="30">
+      <c r="L31" s="22">
         <v>2240</v>
       </c>
-      <c r="M31" s="29">
+      <c r="M31" s="21">
         <v>29</v>
       </c>
-      <c r="N31" s="30">
+      <c r="N31" s="22">
         <v>3970</v>
       </c>
-      <c r="O31" s="29">
+      <c r="O31" s="21">
         <v>16</v>
       </c>
-      <c r="P31" s="30">
+      <c r="P31" s="22">
         <v>2380</v>
       </c>
-      <c r="Q31" s="29">
+      <c r="Q31" s="21">
         <v>19</v>
       </c>
-      <c r="R31" s="30">
+      <c r="R31" s="22">
         <v>3035</v>
       </c>
-      <c r="S31" s="29">
+      <c r="S31" s="21">
         <v>15</v>
       </c>
-      <c r="T31" s="30">
+      <c r="T31" s="22">
         <v>2820</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B35" s="31"/>
-      <c r="C35" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="D35" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="E35" s="33" t="s">
+    <row r="35" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="24"/>
+      <c r="C35" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="F35" s="33" t="s">
+      <c r="F35" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="H35" s="33" t="s">
+      <c r="H35" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="I35" s="33" t="s">
+      <c r="I35" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="J35" s="33" t="s">
+      <c r="J35" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="K35" s="33" t="s">
+      <c r="K35" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="L35" s="33" t="s">
+      <c r="L35" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="M35" s="33" t="s">
+      <c r="M35" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="N35" s="33" t="s">
+      <c r="N35" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="33" t="s">
+      <c r="O35" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="P35" s="33" t="s">
+      <c r="P35" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-    </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="33" t="s">
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" s="24"/>
+      <c r="C36" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="D36" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="E36" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="F36" s="33" t="s">
+      <c r="F36" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="G36" s="33" t="s">
+      <c r="G36" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="H36" s="33" t="s">
+      <c r="H36" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="I36" s="33" t="s">
+      <c r="I36" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="J36" s="33" t="s">
+      <c r="J36" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="K36" s="33" t="s">
+      <c r="K36" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="L36" s="33" t="s">
+      <c r="L36" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="M36" s="33" t="s">
+      <c r="M36" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="N36" s="33" t="s">
+      <c r="N36" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="O36" s="33" t="s">
+      <c r="O36" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="P36" s="33" t="s">
+      <c r="P36" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33" t="s">
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" s="24"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33" t="s">
+      <c r="E37" s="23"/>
+      <c r="F37" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33" t="s">
+      <c r="G37" s="23"/>
+      <c r="H37" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="K37" s="33"/>
-      <c r="L37" s="33" t="s">
+      <c r="I37" s="23"/>
+      <c r="J37" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33" t="s">
+      <c r="K37" s="23"/>
+      <c r="L37" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33" t="s">
+      <c r="M37" s="23"/>
+      <c r="N37" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-    </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="O37" s="23"/>
+      <c r="P37" s="23" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="19">
         <v>28</v>
       </c>
-      <c r="D38" s="28">
+      <c r="D38" s="20">
         <v>6420</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="19">
         <v>5</v>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="20">
         <v>1180</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="19">
         <v>4</v>
       </c>
-      <c r="H38" s="27">
+      <c r="H38" s="19">
         <v>920</v>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="19">
         <v>7</v>
       </c>
-      <c r="J38" s="28">
+      <c r="J38" s="20">
         <v>1760</v>
       </c>
-      <c r="K38" s="27">
+      <c r="K38" s="19">
         <v>3</v>
       </c>
-      <c r="L38" s="27">
+      <c r="L38" s="19">
         <v>640</v>
       </c>
-      <c r="M38" s="27">
+      <c r="M38" s="19">
         <v>5</v>
       </c>
-      <c r="N38" s="28">
+      <c r="N38" s="20">
         <v>1210</v>
       </c>
-      <c r="O38" s="27">
+      <c r="O38" s="19">
         <v>4</v>
       </c>
-      <c r="P38" s="27">
+      <c r="P38" s="19">
         <v>710</v>
       </c>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="19">
         <v>12</v>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="20">
         <v>2685</v>
       </c>
-      <c r="E39" s="27">
+      <c r="E39" s="19">
         <v>2</v>
       </c>
-      <c r="F39" s="27">
+      <c r="F39" s="19">
         <v>420</v>
       </c>
-      <c r="G39" s="27">
+      <c r="G39" s="19">
         <v>2</v>
       </c>
-      <c r="H39" s="27">
+      <c r="H39" s="19">
         <v>350</v>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="19">
         <v>3</v>
       </c>
-      <c r="J39" s="27">
+      <c r="J39" s="19">
         <v>720</v>
       </c>
-      <c r="K39" s="27">
+      <c r="K39" s="19">
         <v>1</v>
       </c>
-      <c r="L39" s="27">
+      <c r="L39" s="19">
         <v>240</v>
       </c>
-      <c r="M39" s="27">
+      <c r="M39" s="19">
         <v>2</v>
       </c>
-      <c r="N39" s="27">
+      <c r="N39" s="19">
         <v>485</v>
       </c>
-      <c r="O39" s="27">
+      <c r="O39" s="19">
         <v>2</v>
       </c>
-      <c r="P39" s="27">
+      <c r="P39" s="19">
         <v>470</v>
       </c>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="26"/>
-      <c r="T39" s="26"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="21">
         <v>40</v>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="22">
         <v>9105</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="21">
         <v>7</v>
       </c>
-      <c r="F40" s="30">
+      <c r="F40" s="22">
         <v>1600</v>
       </c>
-      <c r="G40" s="29">
+      <c r="G40" s="21">
         <v>6</v>
       </c>
-      <c r="H40" s="30">
+      <c r="H40" s="22">
         <v>1270</v>
       </c>
-      <c r="I40" s="29">
-        <v>10</v>
-      </c>
-      <c r="J40" s="30">
+      <c r="I40" s="21">
+        <v>10</v>
+      </c>
+      <c r="J40" s="22">
         <v>2480</v>
       </c>
-      <c r="K40" s="29">
+      <c r="K40" s="21">
         <v>4</v>
       </c>
-      <c r="L40" s="29">
+      <c r="L40" s="21">
         <v>880</v>
       </c>
-      <c r="M40" s="29">
+      <c r="M40" s="21">
         <v>7</v>
       </c>
-      <c r="N40" s="30">
+      <c r="N40" s="22">
         <v>1695</v>
       </c>
-      <c r="O40" s="29">
+      <c r="O40" s="21">
         <v>6</v>
       </c>
-      <c r="P40" s="30">
+      <c r="P40" s="22">
         <v>1180</v>
       </c>
-      <c r="Q40" s="26"/>
-      <c r="R40" s="26"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="W4:Z4"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="AE4:AH4"/>
-    <mergeCell ref="AI4:AL4"/>
-    <mergeCell ref="AM4:AP4"/>
+  <mergeCells count="16">
     <mergeCell ref="AQ4:AT4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:F4"/>
@@ -13509,6 +13489,15 @@
     <mergeCell ref="K4:N4"/>
     <mergeCell ref="O4:R4"/>
     <mergeCell ref="S4:V4"/>
+    <mergeCell ref="W4:Z4"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI4:AL4"/>
+    <mergeCell ref="AM4:AP4"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="B24:B26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/IRA_flat_singlefolder/Other_Tables.xlsx
+++ b/IRA_flat_singlefolder/Other_Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yavnv\Downloads\IRA_Final_18Sept26_3\IRA_flat_singlefolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4763D4-2B41-40AC-9083-3F0E6C2D44E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB944D22-0D91-4041-ABFF-72BF48EDC8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{6C3792BD-ED8C-4773-AE5D-109238BEF1B8}"/>
   </bookViews>
@@ -715,9 +715,6 @@
     <t>Shortfall against securities/margin trading:</t>
   </si>
   <si>
-    <t>Total client</t>
-  </si>
-  <si>
     <t>Total Amount (USD'000)</t>
   </si>
   <si>
@@ -743,6 +740,9 @@
   </si>
   <si>
     <t>client</t>
+  </si>
+  <si>
+    <t>Total clients</t>
   </si>
 </sst>
 </file>
@@ -840,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -888,10 +888,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -901,6 +898,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -913,10 +916,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1241,10 +1240,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="29"/>
+      <c r="C2" s="30"/>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
     </row>
@@ -1539,10 +1538,10 @@
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="29"/>
+      <c r="C40" s="30"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
@@ -1833,10 +1832,10 @@
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B78" s="29" t="s">
+      <c r="B78" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C78" s="29"/>
+      <c r="C78" s="30"/>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
@@ -2127,10 +2126,10 @@
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="29" t="s">
+      <c r="B116" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C116" s="29"/>
+      <c r="C116" s="30"/>
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
     </row>
@@ -2425,22 +2424,22 @@
       </c>
     </row>
     <row r="156" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B156" s="30" t="s">
+      <c r="B156" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C156" s="30"/>
-      <c r="D156" s="30"/>
-      <c r="E156" s="30"/>
-      <c r="F156" s="30"/>
-      <c r="G156" s="30"/>
-      <c r="H156" s="30"/>
-      <c r="I156" s="30"/>
-      <c r="J156" s="30"/>
-      <c r="K156" s="30"/>
-      <c r="L156" s="30"/>
-      <c r="M156" s="30"/>
-      <c r="N156" s="30"/>
-      <c r="O156" s="30"/>
+      <c r="C156" s="31"/>
+      <c r="D156" s="31"/>
+      <c r="E156" s="31"/>
+      <c r="F156" s="31"/>
+      <c r="G156" s="31"/>
+      <c r="H156" s="31"/>
+      <c r="I156" s="31"/>
+      <c r="J156" s="31"/>
+      <c r="K156" s="31"/>
+      <c r="L156" s="31"/>
+      <c r="M156" s="31"/>
+      <c r="N156" s="31"/>
+      <c r="O156" s="31"/>
       <c r="P156" s="2"/>
     </row>
     <row r="157" spans="2:16" x14ac:dyDescent="0.3">
@@ -3504,22 +3503,22 @@
       </c>
     </row>
     <row r="195" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B195" s="32" t="s">
+      <c r="B195" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C195" s="32"/>
-      <c r="D195" s="32"/>
-      <c r="E195" s="32"/>
-      <c r="F195" s="32"/>
-      <c r="G195" s="32"/>
-      <c r="H195" s="32"/>
-      <c r="I195" s="32"/>
-      <c r="J195" s="32"/>
-      <c r="K195" s="32"/>
-      <c r="L195" s="32"/>
-      <c r="M195" s="32"/>
-      <c r="N195" s="32"/>
-      <c r="O195" s="32"/>
+      <c r="C195" s="33"/>
+      <c r="D195" s="33"/>
+      <c r="E195" s="33"/>
+      <c r="F195" s="33"/>
+      <c r="G195" s="33"/>
+      <c r="H195" s="33"/>
+      <c r="I195" s="33"/>
+      <c r="J195" s="33"/>
+      <c r="K195" s="33"/>
+      <c r="L195" s="33"/>
+      <c r="M195" s="33"/>
+      <c r="N195" s="33"/>
+      <c r="O195" s="33"/>
     </row>
     <row r="196" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B196" s="1" t="s">
@@ -4582,22 +4581,22 @@
       </c>
     </row>
     <row r="233" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B233" s="30" t="s">
+      <c r="B233" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="C233" s="30"/>
-      <c r="D233" s="30"/>
-      <c r="E233" s="30"/>
-      <c r="F233" s="30"/>
-      <c r="G233" s="30"/>
-      <c r="H233" s="30"/>
-      <c r="I233" s="30"/>
-      <c r="J233" s="30"/>
-      <c r="K233" s="30"/>
-      <c r="L233" s="30"/>
-      <c r="M233" s="30"/>
-      <c r="N233" s="30"/>
-      <c r="O233" s="30"/>
+      <c r="C233" s="31"/>
+      <c r="D233" s="31"/>
+      <c r="E233" s="31"/>
+      <c r="F233" s="31"/>
+      <c r="G233" s="31"/>
+      <c r="H233" s="31"/>
+      <c r="I233" s="31"/>
+      <c r="J233" s="31"/>
+      <c r="K233" s="31"/>
+      <c r="L233" s="31"/>
+      <c r="M233" s="31"/>
+      <c r="N233" s="31"/>
+      <c r="O233" s="31"/>
       <c r="P233" s="2"/>
     </row>
     <row r="234" spans="2:16" x14ac:dyDescent="0.3">
@@ -5661,22 +5660,22 @@
       </c>
     </row>
     <row r="272" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B272" s="30" t="s">
+      <c r="B272" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="C272" s="30"/>
-      <c r="D272" s="30"/>
-      <c r="E272" s="30"/>
-      <c r="F272" s="30"/>
-      <c r="G272" s="30"/>
-      <c r="H272" s="30"/>
-      <c r="I272" s="30"/>
-      <c r="J272" s="30"/>
-      <c r="K272" s="30"/>
-      <c r="L272" s="30"/>
-      <c r="M272" s="30"/>
-      <c r="N272" s="30"/>
-      <c r="O272" s="30"/>
+      <c r="C272" s="31"/>
+      <c r="D272" s="31"/>
+      <c r="E272" s="31"/>
+      <c r="F272" s="31"/>
+      <c r="G272" s="31"/>
+      <c r="H272" s="31"/>
+      <c r="I272" s="31"/>
+      <c r="J272" s="31"/>
+      <c r="K272" s="31"/>
+      <c r="L272" s="31"/>
+      <c r="M272" s="31"/>
+      <c r="N272" s="31"/>
+      <c r="O272" s="31"/>
     </row>
     <row r="273" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B273" s="1" t="s">
@@ -6739,13 +6738,13 @@
       </c>
     </row>
     <row r="311" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B311" s="31" t="s">
+      <c r="B311" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C311" s="31"/>
-      <c r="D311" s="31"/>
-      <c r="E311" s="31"/>
-      <c r="F311" s="31"/>
+      <c r="C311" s="32"/>
+      <c r="D311" s="32"/>
+      <c r="E311" s="32"/>
+      <c r="F311" s="32"/>
     </row>
     <row r="312" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B312" s="5" t="s">
@@ -12268,78 +12267,78 @@
       </c>
     </row>
     <row r="4" spans="2:46" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="26" t="s">
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="26" t="s">
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="26" t="s">
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="26" t="s">
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="26" t="s">
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="26" t="s">
+      <c r="X4" s="26"/>
+      <c r="Y4" s="26"/>
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="26" t="s">
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="27"/>
-      <c r="AH4" s="27"/>
-      <c r="AI4" s="26" t="s">
+      <c r="AF4" s="26"/>
+      <c r="AG4" s="26"/>
+      <c r="AH4" s="26"/>
+      <c r="AI4" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="27"/>
-      <c r="AL4" s="27"/>
-      <c r="AM4" s="26" t="s">
+      <c r="AJ4" s="26"/>
+      <c r="AK4" s="26"/>
+      <c r="AL4" s="26"/>
+      <c r="AM4" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="AN4" s="27"/>
-      <c r="AO4" s="27"/>
-      <c r="AP4" s="27"/>
-      <c r="AQ4" s="26" t="s">
+      <c r="AN4" s="26"/>
+      <c r="AO4" s="26"/>
+      <c r="AP4" s="26"/>
+      <c r="AQ4" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="AR4" s="27"/>
-      <c r="AS4" s="27"/>
-      <c r="AT4" s="27"/>
+      <c r="AR4" s="26"/>
+      <c r="AS4" s="26"/>
+      <c r="AT4" s="26"/>
     </row>
     <row r="5" spans="2:46" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="15" t="s">
         <v>213</v>
       </c>
@@ -12772,12 +12771,12 @@
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B24" s="24"/>
-      <c r="C24" s="24" t="s">
+      <c r="B24" s="28"/>
+      <c r="C24" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="D24" s="29" t="s">
         <v>228</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>229</v>
       </c>
       <c r="E24" s="23" t="s">
         <v>57</v>
@@ -12810,10 +12809,10 @@
         <v>5</v>
       </c>
       <c r="O24" s="23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P24" s="23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>7</v>
@@ -12822,100 +12821,100 @@
         <v>7</v>
       </c>
       <c r="S24" s="23" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T24" s="23" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="25"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="29"/>
       <c r="E25" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="F25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="F25" s="23" t="s">
-        <v>231</v>
-      </c>
       <c r="G25" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="H25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="H25" s="23" t="s">
-        <v>231</v>
-      </c>
       <c r="I25" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="J25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="J25" s="23" t="s">
-        <v>231</v>
-      </c>
       <c r="K25" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="L25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="L25" s="23" t="s">
-        <v>231</v>
-      </c>
       <c r="M25" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="N25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="N25" s="23" t="s">
-        <v>231</v>
-      </c>
       <c r="O25" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="P25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="P25" s="23" t="s">
-        <v>231</v>
-      </c>
       <c r="Q25" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="R25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="R25" s="23" t="s">
-        <v>231</v>
-      </c>
       <c r="S25" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="T25" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="T25" s="23" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
       <c r="E26" s="23"/>
       <c r="F26" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I26" s="23"/>
       <c r="J26" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K26" s="23"/>
       <c r="L26" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M26" s="23"/>
       <c r="N26" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O26" s="23"/>
       <c r="P26" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q26" s="23"/>
       <c r="R26" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S26" s="23"/>
       <c r="T26" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
@@ -13215,15 +13214,15 @@
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="24"/>
-      <c r="C35" s="33" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="34" t="s">
+      <c r="D35" s="24" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="23" t="s">
@@ -13264,79 +13263,79 @@
       </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B36" s="24"/>
-      <c r="C36" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="D36" s="34" t="s">
+      <c r="B36" s="28"/>
+      <c r="C36" s="23" t="s">
         <v>236</v>
       </c>
+      <c r="D36" s="24" t="s">
+        <v>235</v>
+      </c>
       <c r="E36" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="F36" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="F36" s="23" t="s">
+      <c r="G36" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="J36" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="K36" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="L36" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="M36" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="N36" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="O36" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="P36" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" s="28"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="24" t="s">
         <v>231</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="J36" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="K36" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="L36" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="N36" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="O36" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="P36" s="23" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B37" s="24"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34" t="s">
-        <v>232</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I37" s="23"/>
       <c r="J37" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K37" s="23"/>
       <c r="L37" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M37" s="23"/>
       <c r="N37" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O37" s="23"/>
       <c r="P37" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
@@ -13482,6 +13481,10 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="B24:B26"/>
     <mergeCell ref="AQ4:AT4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:F4"/>
@@ -13494,10 +13497,6 @@
     <mergeCell ref="AE4:AH4"/>
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="AM4:AP4"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="B24:B26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
